--- a/public/templates/convenio.xlsx
+++ b/public/templates/convenio.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="Rea3c2efa64bb4e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="R35b321aa69834232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="R94df6a8ff48c4e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="R1ad677b0172e4cae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="R89b5d89f0844426c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="R6bac2cc173c8422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="Ree5a655f49c94a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="Rc8ed6fc0d2fd4ca2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="Rc0c5e9086fbb4d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores_Cedidos" sheetId="10" r:id="R95778fc12f6e49ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Cedidos" sheetId="11" r:id="Reb77a3d6cfc247ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="12" r:id="Raff1eb42d37f4d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orientacoes" sheetId="1" r:id="Ra645b6f95a024bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste" sheetId="2" r:id="R1c901d9975154c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratos" sheetId="3" r:id="Ra2434752570244a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naturezas_Contrato" sheetId="4" r:id="Ra23c17ad28da4b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documentos_Fiscais" sheetId="5" r:id="Rf3de80ba87ff4ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagamentos" sheetId="6" r:id="R67967d3330534034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionarios" sheetId="7" r:id="R371c04aba05e44e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salarios" sheetId="8" r:id="R240aeff8dbff4c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Func" sheetId="9" r:id="R7bfa7f314c1e4760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores_Cedidos" sheetId="10" r:id="R9913630a10914fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remuneracoes_Cedidos" sheetId="11" r:id="Rb507b89ae118431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="12" r:id="Rf1d4f8c21ed1491c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -401,10 +401,10 @@
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
       <x:c r="A11" s="1" t="str">
-        <x:v>CSV alternativo</x:v>
+        <x:v>Arquivo de carga</x:v>
       </x:c>
       <x:c r="B11" s="1" t="str">
-        <x:v>Um CSV UTF-8 por aba. Use o nome da aba como nome do arquivo. Ajuste.csv é obrigatório.</x:v>
+        <x:v>Envie somente um arquivo XLSX com todas as abas do ajuste.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
